--- a/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_2/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,11 +509,57 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be processed in the analytical module, improving the scalability and availability of the system.</t>
+          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6038</v>
+        <v>0.6364</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Speed and latency</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>It is the set of cloud computing services that allows the creation of scalable and highly available applications. The use of AWS was decided and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6771</v>
       </c>
     </row>
   </sheetData>
